--- a/artfynd/A 39007-2025 artfynd.xlsx
+++ b/artfynd/A 39007-2025 artfynd.xlsx
@@ -2267,7 +2267,7 @@
         <v>127025076</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>127025078</v>
       </c>
       <c r="B18" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>127025077</v>
       </c>
       <c r="B19" t="n">
-        <v>80993</v>
+        <v>80995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39007-2025 artfynd.xlsx
+++ b/artfynd/A 39007-2025 artfynd.xlsx
@@ -2267,7 +2267,7 @@
         <v>127025076</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>127025078</v>
       </c>
       <c r="B18" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>127025077</v>
       </c>
       <c r="B19" t="n">
-        <v>80995</v>
+        <v>80986</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39007-2025 artfynd.xlsx
+++ b/artfynd/A 39007-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79091908</v>
+        <v>126498570</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnsjöberget norra, Hjd</t>
+          <t>Björnsjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415298.061559447</v>
+        <v>415335</v>
       </c>
       <c r="R2" t="n">
-        <v>6970568.072728236</v>
+        <v>6970830</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Silverved av tall</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,31 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79091919</v>
+        <v>79112742</v>
       </c>
       <c r="B3" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnsjöberget norra, Hjd</t>
+          <t>Björnsjöberget N, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415379.0117577548</v>
+        <v>415266</v>
       </c>
       <c r="R3" t="n">
-        <v>6970708.962909659</v>
+        <v>6970573</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,24 +840,9 @@
           <t>2019-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
+          <t>Linda Johannesson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -917,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79112751</v>
+        <v>126498568</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnsjöberget N, Hjd</t>
+          <t>Björnsjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415282.8541288208</v>
+        <v>415151</v>
       </c>
       <c r="R4" t="n">
-        <v>6970546.0815752</v>
+        <v>6970685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,31 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Martin Westberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79112742</v>
+        <v>126498574</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,14 +1001,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnsjöberget N, Hjd</t>
+          <t>Björnsjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415266.1550272781</v>
+        <v>415227</v>
       </c>
       <c r="R5" t="n">
-        <v>6970572.552325659</v>
+        <v>6970703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,31 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Martin Westberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79112758</v>
+        <v>126513279</v>
       </c>
       <c r="B6" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,34 +1078,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnsjöberget N, Hjd</t>
+          <t>Björnsjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415284.2492171661</v>
+        <v>415339</v>
       </c>
       <c r="R6" t="n">
-        <v>6970546.959152102</v>
+        <v>6970348</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,26 +1152,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Martin Westberg</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126498568</v>
+        <v>126513280</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415151</v>
+        <v>415404</v>
       </c>
       <c r="R7" t="n">
-        <v>6970685</v>
+        <v>6970399</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,22 +1253,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126498566</v>
+        <v>127025078</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,34 +1280,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnsjöberget, Hjd</t>
+          <t>LÃ¶vdalen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415301</v>
+        <v>415812</v>
       </c>
       <c r="R8" t="n">
-        <v>6970592</v>
+        <v>6970528</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,12 +1338,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1368,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126498567</v>
+        <v>126512445</v>
       </c>
       <c r="B9" t="n">
-        <v>92727</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415151</v>
+        <v>415537</v>
       </c>
       <c r="R9" t="n">
-        <v>6970685</v>
+        <v>6970468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,22 +1465,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126498565</v>
+        <v>127025077</v>
       </c>
       <c r="B10" t="n">
-        <v>78738</v>
+        <v>81312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1492,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnsjöberget, Hjd</t>
+          <t>LÃ¶vdalen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415453</v>
+        <v>415664</v>
       </c>
       <c r="R10" t="n">
-        <v>6970632</v>
+        <v>6970588</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,12 +1550,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1580,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126513278</v>
+        <v>126513662</v>
       </c>
       <c r="B11" t="n">
-        <v>5492</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101410</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>415289</v>
+        <v>415400</v>
       </c>
       <c r="R11" t="n">
-        <v>6970301</v>
+        <v>6970086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,48 +1693,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126513661</v>
+        <v>79091930</v>
       </c>
       <c r="B12" t="n">
-        <v>92727</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnsjöberget, Hjd</t>
+          <t>Björnsjöberget norra, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>415358</v>
+        <v>415359</v>
       </c>
       <c r="R12" t="n">
-        <v>6970283</v>
+        <v>6970677</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,12 +1758,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,26 +1783,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126512445</v>
+        <v>79091919</v>
       </c>
       <c r="B13" t="n">
-        <v>80955</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,37 +1810,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnsjöberget, Hjd</t>
+          <t>Björnsjöberget norra, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>415537</v>
+        <v>415379</v>
       </c>
       <c r="R13" t="n">
-        <v>6970468</v>
+        <v>6970709</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1925,12 +1864,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,26 +1889,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126513281</v>
+        <v>126498567</v>
       </c>
       <c r="B14" t="n">
-        <v>79569</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +1916,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>415415</v>
+        <v>415151</v>
       </c>
       <c r="R14" t="n">
-        <v>6970380</v>
+        <v>6970685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,26 +1990,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126512442</v>
+        <v>126498573</v>
       </c>
       <c r="B15" t="n">
-        <v>91263</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,21 +2013,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>415471</v>
+        <v>415227</v>
       </c>
       <c r="R15" t="n">
-        <v>6970535</v>
+        <v>6970703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,26 +2087,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126512443</v>
+        <v>126513661</v>
       </c>
       <c r="B16" t="n">
-        <v>75075</v>
+        <v>91962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>415498</v>
+        <v>415358</v>
       </c>
       <c r="R16" t="n">
-        <v>6970529</v>
+        <v>6970283</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025076</v>
+        <v>79091941</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,41 +2211,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>LÃ¶vdalen, Hjd</t>
+          <t>Björnsjöberget norra, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>415691</v>
+        <v>415355</v>
       </c>
       <c r="R17" t="n">
-        <v>6970518</v>
+        <v>6970740</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2333,22 +2265,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,22 +2290,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127025078</v>
+        <v>79112748</v>
       </c>
       <c r="B18" t="n">
-        <v>78687</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,38 +2317,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>LÃ¶vdalen, Hjd</t>
+          <t>Björnsjöberget N, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>415812</v>
+        <v>415332</v>
       </c>
       <c r="R18" t="n">
-        <v>6970528</v>
+        <v>6970797</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,22 +2371,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,22 +2391,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Linda Johannesson, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127025077</v>
+        <v>126512443</v>
       </c>
       <c r="B19" t="n">
-        <v>80995</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,41 +2418,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>LÃ¶vdalen, Hjd</t>
+          <t>Björnsjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>415664</v>
+        <v>415498</v>
       </c>
       <c r="R19" t="n">
-        <v>6970588</v>
+        <v>6970529</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2555,22 +2472,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2585,15 +2492,1359 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126498565</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björnsjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>415453</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6970632</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>79091895</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Björnsjöberget norra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>415356</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6970736</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Silverved av tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>79112719</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björnsjöberget N, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>415346</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6970760</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>79112751</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Björnsjöberget N, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>415283</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6970546</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126498566</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Björnsjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>415301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6970592</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127025076</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>LÃ¶vdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>415691</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6970518</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126513278</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Björnsjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>415289</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6970301</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>79091920</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Björnsjöberget norra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>415351</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6970730</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>79091908</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Björnsjöberget norra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>415298</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6970568</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Silverved av tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>79091910</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Björnsjöberget norra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>415317</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6970788</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Silverved av tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Götmark, Linnea Helmersson, Martin Westberg, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>79112728</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Björnsjöberget N, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>415337</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6970795</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>79112758</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Björnsjöberget N, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>415284</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6970547</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126513281</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Björnsjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>415415</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6970380</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
